--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$63</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2067" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="255">
   <si>
     <t>Property</t>
   </si>
@@ -39,13 +39,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>EASMailboxMSS</t>
+    <t>AsMailboxMSSExtension</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>EAS Mailbox MSS</t>
+    <t>AS Mailbox MSS Extension</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:12:13+00:00</t>
+    <t>2023-04-13T08:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -421,13 +421,14 @@
 PER pour une BAL personnelle, rattachée à une personne physique</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>Type de  boîte aux lettre MSS</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J139-TypeBAL-RASS/FHIR/JDV-J139-TypeBAL-RASS</t>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
   </si>
   <si>
     <t>Extension.extension:type.value[x].id</t>
@@ -629,6 +630,18 @@
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>Extension.extension:type.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J139-TypeBAL-RASS/FHIR/JDV-J139-TypeBAL-RASS</t>
   </si>
   <si>
     <t>Extension.extension:description</t>
@@ -1121,12 +1134,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AK63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.65625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="54.2421875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.94140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2582,28 +2595,26 @@
         <v>76</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y14" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="Z14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB14" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AC14" s="2"/>
+      <c r="AD14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE14" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>120</v>
@@ -3792,7 +3803,7 @@
         <v>199</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>200</v>
@@ -3808,7 +3819,7 @@
         <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>76</v>
@@ -3817,13 +3828,13 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3850,13 +3861,11 @@
         <v>76</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>76</v>
+        <v>202</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>76</v>
@@ -3874,32 +3883,34 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>76</v>
       </c>
@@ -3911,7 +3922,7 @@
         <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>76</v>
@@ -3920,13 +3931,13 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3977,30 +3988,30 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4011,7 +4022,7 @@
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>76</v>
@@ -4023,13 +4034,13 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4068,42 +4079,42 @@
         <v>76</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4111,10 +4122,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>76</v>
@@ -4126,24 +4137,22 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>200</v>
+        <v>76</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>76</v>
@@ -4173,42 +4182,42 @@
         <v>76</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4216,7 +4225,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>82</v>
@@ -4231,22 +4240,24 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>205</v>
+        <v>112</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>76</v>
+        <v>204</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>76</v>
@@ -4288,19 +4299,19 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>99</v>
@@ -4308,14 +4319,12 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>76</v>
       </c>
@@ -4327,7 +4336,7 @@
         <v>82</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>76</v>
@@ -4336,13 +4345,13 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>28</v>
+        <v>209</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4393,32 +4402,34 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="D32" t="s" s="2">
         <v>76</v>
       </c>
@@ -4430,7 +4441,7 @@
         <v>82</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>76</v>
@@ -4439,13 +4450,13 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4496,30 +4507,30 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4530,7 +4541,7 @@
         <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>76</v>
@@ -4542,13 +4553,13 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4587,42 +4598,42 @@
         <v>76</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4630,10 +4641,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>76</v>
@@ -4645,24 +4656,22 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>207</v>
+        <v>76</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>76</v>
@@ -4692,42 +4701,42 @@
         <v>76</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4735,7 +4744,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>82</v>
@@ -4750,22 +4759,24 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>212</v>
+        <v>112</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>76</v>
+        <v>211</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>76</v>
@@ -4807,19 +4818,19 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>99</v>
@@ -4827,14 +4838,12 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>76</v>
       </c>
@@ -4846,7 +4855,7 @@
         <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>76</v>
@@ -4855,13 +4864,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>28</v>
+        <v>216</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4912,32 +4921,34 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="D37" t="s" s="2">
         <v>76</v>
       </c>
@@ -4949,7 +4960,7 @@
         <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>76</v>
@@ -4958,13 +4969,13 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5015,30 +5026,30 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5049,7 +5060,7 @@
         <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>76</v>
@@ -5061,13 +5072,13 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5106,42 +5117,42 @@
         <v>76</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5149,10 +5160,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>76</v>
@@ -5164,24 +5175,22 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>214</v>
+        <v>76</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>76</v>
@@ -5211,42 +5220,42 @@
         <v>76</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5254,7 +5263,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>82</v>
@@ -5269,22 +5278,24 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>219</v>
+        <v>112</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>76</v>
+        <v>218</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>76</v>
@@ -5326,19 +5337,19 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>99</v>
@@ -5346,14 +5357,12 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>76</v>
       </c>
@@ -5365,7 +5374,7 @@
         <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>76</v>
@@ -5374,13 +5383,13 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5431,32 +5440,34 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>76</v>
       </c>
@@ -5468,7 +5479,7 @@
         <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>76</v>
@@ -5477,13 +5488,13 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5534,30 +5545,30 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5568,7 +5579,7 @@
         <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>76</v>
@@ -5580,13 +5591,13 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5625,42 +5636,42 @@
         <v>76</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5668,10 +5679,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>76</v>
@@ -5683,24 +5694,22 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>221</v>
+        <v>76</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>76</v>
@@ -5730,42 +5739,42 @@
         <v>76</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5773,7 +5782,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>82</v>
@@ -5788,22 +5797,24 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>226</v>
+        <v>112</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>76</v>
+        <v>225</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>76</v>
@@ -5845,19 +5856,19 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>99</v>
@@ -5865,14 +5876,12 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>76</v>
       </c>
@@ -5884,7 +5893,7 @@
         <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>76</v>
@@ -5893,13 +5902,13 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>28</v>
+        <v>230</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5950,32 +5959,34 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="D47" t="s" s="2">
         <v>76</v>
       </c>
@@ -5987,7 +5998,7 @@
         <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>76</v>
@@ -5996,13 +6007,13 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6053,30 +6064,30 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6087,7 +6098,7 @@
         <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>76</v>
@@ -6099,13 +6110,13 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6144,42 +6155,42 @@
         <v>76</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6187,10 +6198,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>76</v>
@@ -6202,24 +6213,22 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>228</v>
+        <v>76</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>76</v>
@@ -6249,42 +6258,42 @@
         <v>76</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6292,7 +6301,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>82</v>
@@ -6307,16 +6316,16 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>184</v>
+        <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>233</v>
+        <v>112</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>234</v>
+        <v>114</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6324,7 +6333,7 @@
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>76</v>
+        <v>232</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>76</v>
@@ -6366,19 +6375,19 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>99</v>
@@ -6386,14 +6395,12 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>76</v>
       </c>
@@ -6405,7 +6412,7 @@
         <v>82</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>76</v>
@@ -6414,15 +6421,17 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>90</v>
+        <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>28</v>
+        <v>237</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>119</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>76</v>
@@ -6471,32 +6480,34 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>76</v>
       </c>
@@ -6508,7 +6519,7 @@
         <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>76</v>
@@ -6517,13 +6528,13 @@
         <v>76</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6574,30 +6585,30 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6608,7 +6619,7 @@
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>76</v>
@@ -6620,13 +6631,13 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6665,42 +6676,42 @@
         <v>76</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6708,10 +6719,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>76</v>
@@ -6723,24 +6734,22 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>236</v>
+        <v>76</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>76</v>
@@ -6770,42 +6779,42 @@
         <v>76</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6813,7 +6822,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>82</v>
@@ -6828,16 +6837,16 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>184</v>
+        <v>111</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>241</v>
+        <v>112</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>242</v>
+        <v>114</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -6845,7 +6854,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>76</v>
+        <v>240</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>76</v>
@@ -6887,19 +6896,19 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>99</v>
@@ -6907,14 +6916,12 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>76</v>
       </c>
@@ -6923,10 +6930,10 @@
         <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>76</v>
@@ -6935,15 +6942,17 @@
         <v>76</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>90</v>
+        <v>184</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>28</v>
+        <v>245</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>119</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -6992,32 +7001,34 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="D57" t="s" s="2">
         <v>76</v>
       </c>
@@ -7026,7 +7037,7 @@
         <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>76</v>
@@ -7038,13 +7049,13 @@
         <v>76</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7095,30 +7106,30 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7129,7 +7140,7 @@
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>76</v>
@@ -7141,13 +7152,13 @@
         <v>76</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7186,42 +7197,42 @@
         <v>76</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7229,10 +7240,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>76</v>
@@ -7244,24 +7255,22 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>244</v>
+        <v>76</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>76</v>
@@ -7291,42 +7300,42 @@
         <v>76</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7334,7 +7343,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>82</v>
@@ -7349,22 +7358,24 @@
         <v>76</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>249</v>
+        <v>111</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>76</v>
+        <v>248</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>76</v>
@@ -7406,19 +7417,19 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>99</v>
@@ -7426,10 +7437,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>115</v>
+        <v>252</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7437,7 +7448,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>82</v>
@@ -7452,24 +7463,22 @@
         <v>76</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>111</v>
+        <v>253</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>76</v>
@@ -7511,19 +7520,19 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>99</v>
@@ -7531,10 +7540,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7542,10 +7551,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>76</v>
@@ -7557,22 +7566,24 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>250</v>
+        <v>111</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>76</v>
@@ -7614,26 +7625,129 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>99</v>
       </c>
     </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AK62">
+  <autoFilter ref="A1:AK63">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7643,7 +7757,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI61">
+  <conditionalFormatting sqref="A2:AI62">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$56</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="196">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:22:34+00:00</t>
+    <t>2023-04-13T08:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -413,6 +413,19 @@
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>Extension.extension:type.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
   </si>
   <si>
     <t>Valeurs possibles :
@@ -421,329 +434,134 @@
 PER pour une BAL personnelle, rattachée à une personne physique</t>
   </si>
   <si>
+    <t>required</t>
+  </si>
+  <si>
     <t>Type de  boîte aux lettre MSS</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.value[x].id</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.value[x].extension</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.value[x].coding</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R257-TypeBAL/FHIR/TRE-R257-TypeBAL</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].coding.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].coding.userSelected</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J139-TypeBAL-RASS/FHIR/JDV-J139-TypeBAL-RASS</t>
+  </si>
+  <si>
+    <t>Extension.extension:description</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>Extension.extension:description.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:description.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:description.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:description.value[x]</t>
+  </si>
+  <si>
+    <t>Description fonctionnelle de la boîte aux lettres</t>
+  </si>
+  <si>
+    <t>Extension.extension:responsible</t>
+  </si>
+  <si>
+    <t>responsible</t>
+  </si>
+  <si>
+    <t>Extension.extension:responsible.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:responsible.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:responsible.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:responsible.value[x]</t>
+  </si>
+  <si>
+    <t>Texte libre donnant les coordonnées de la (ou des) personne(s) responsable(s) au niveau opérationnel de la boîte aux lettres. Non renseigné pour les types de boîte aux lettres "PER".</t>
+  </si>
+  <si>
+    <t>Extension.extension:service</t>
+  </si>
+  <si>
+    <t>service</t>
+  </si>
+  <si>
+    <t>Extension.extension:service.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:service.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:service.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:service.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:service.value[x]:valueString</t>
+  </si>
+  <si>
+    <t>valueString</t>
+  </si>
+  <si>
+    <t>Nom et description du service de rattachement de l’utilisateur de la boîte aux lettres dans l’organisation.</t>
+  </si>
+  <si>
+    <t>Extension.extension:phone</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>Extension.extension:phone.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:phone.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:phone.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:phone.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:phone.value[x]:valueString</t>
+  </si>
+  <si>
+    <t>Coordonnées téléphoniques spécifiques à l’usage de la boîte aux lettres MSSanté</t>
+  </si>
+  <si>
+    <t>Extension.extension:digitization</t>
+  </si>
+  <si>
+    <t>digitization</t>
+  </si>
+  <si>
+    <t>Extension.extension:digitization.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:digitization.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:digitization.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:digitization.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
 </t>
   </si>
   <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.value[x].text</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J139-TypeBAL-RASS/FHIR/JDV-J139-TypeBAL-RASS</t>
-  </si>
-  <si>
-    <t>Extension.extension:description</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>Extension.extension:description.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:description.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:description.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:description.value[x]</t>
-  </si>
-  <si>
-    <t>Description fonctionnelle de la boîte aux lettres</t>
-  </si>
-  <si>
-    <t>Extension.extension:responsible</t>
-  </si>
-  <si>
-    <t>responsible</t>
-  </si>
-  <si>
-    <t>Extension.extension:responsible.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:responsible.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:responsible.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:responsible.value[x]</t>
-  </si>
-  <si>
-    <t>Texte libre donnant les coordonnées de la (ou des) personne(s) responsable(s) au niveau opérationnel de la boîte aux lettres. Non renseigné pour les types de boîte aux lettres "PER".</t>
-  </si>
-  <si>
-    <t>Extension.extension:service</t>
-  </si>
-  <si>
-    <t>service</t>
-  </si>
-  <si>
-    <t>Extension.extension:service.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:service.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:service.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:service.value[x]</t>
-  </si>
-  <si>
-    <t>Nom et description du service de rattachement de l’utilisateur de la boîte aux lettres dans l’organisation.</t>
-  </si>
-  <si>
-    <t>Extension.extension:phone</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>Extension.extension:phone.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:phone.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:phone.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:phone.value[x]</t>
-  </si>
-  <si>
-    <t>Coordonnées téléphoniques spécifiques à l’usage de la boîte aux lettres MSSanté</t>
-  </si>
-  <si>
-    <t>Extension.extension:digitization</t>
-  </si>
-  <si>
-    <t>digitization</t>
-  </si>
-  <si>
-    <t>Extension.extension:digitization.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:digitization.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:digitization.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:digitization.value[x]</t>
+    <t>Extension.extension:digitization.value[x]:valueBoolean</t>
+  </si>
+  <si>
+    <t>valueBoolean</t>
   </si>
   <si>
     <t>Indicateur d’acceptation de la dématérialisation (ou « Zéro papier »</t>
@@ -769,6 +587,9 @@
   </si>
   <si>
     <t>Extension.extension:publication.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:publication.value[x]:valueBoolean</t>
   </si>
   <si>
     <t>ndicateur liste rouge</t>
@@ -1134,11 +955,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK63"/>
+  <dimension ref="A1:AK56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.2421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.94140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="29.1484375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -1151,7 +972,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="229.41796875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -1168,11 +989,11 @@
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="23.95703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="18.1875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="46.53125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.98046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2568,7 +2389,7 @@
         <v>118</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2598,7 +2419,7 @@
         <v>76</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="Z14" t="s" s="2">
         <v>76</v>
@@ -2607,14 +2428,14 @@
         <v>76</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>120</v>
@@ -2637,12 +2458,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>76</v>
       </c>
@@ -2663,13 +2486,13 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2696,13 +2519,13 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>76</v>
@@ -2720,7 +2543,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2729,35 +2552,37 @@
         <v>82</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>76</v>
@@ -2769,14 +2594,12 @@
         <v>90</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -2813,16 +2636,16 @@
         <v>76</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>97</v>
@@ -2840,15 +2663,15 @@
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2859,7 +2682,7 @@
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>76</v>
@@ -2868,23 +2691,19 @@
         <v>76</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>76</v>
       </c>
@@ -2932,30 +2751,30 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>144</v>
+        <v>86</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>145</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2966,7 +2785,7 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>76</v>
@@ -2978,13 +2797,13 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3023,53 +2842,53 @@
         <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>76</v>
@@ -3081,16 +2900,16 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3098,7 +2917,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>76</v>
@@ -3128,31 +2947,31 @@
         <v>76</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>99</v>
@@ -3160,10 +2979,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3183,29 +3002,25 @@
         <v>76</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>76</v>
@@ -3247,7 +3062,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3262,17 +3077,19 @@
         <v>121</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>158</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>76</v>
       </c>
@@ -3284,26 +3101,24 @@
         <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>161</v>
+        <v>28</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3352,30 +3167,30 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>164</v>
+        <v>97</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>165</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3395,23 +3210,19 @@
         <v>76</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>76</v>
       </c>
@@ -3459,7 +3270,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>173</v>
+        <v>86</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3468,21 +3279,21 @@
         <v>82</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>174</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3493,7 +3304,7 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>76</v>
@@ -3502,23 +3313,19 @@
         <v>76</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>177</v>
+        <v>28</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>76</v>
       </c>
@@ -3554,42 +3361,42 @@
         <v>76</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>181</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>183</v>
+        <v>110</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3597,7 +3404,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>82</v>
@@ -3609,29 +3416,27 @@
         <v>76</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>184</v>
+        <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>186</v>
+        <v>113</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>76</v>
@@ -3673,30 +3478,30 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>189</v>
+        <v>115</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>190</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>192</v>
+        <v>117</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3716,23 +3521,19 @@
         <v>76</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>76</v>
       </c>
@@ -3780,7 +3581,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>197</v>
+        <v>120</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3795,18 +3596,18 @@
         <v>121</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>198</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>199</v>
+        <v>151</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>76</v>
@@ -3819,7 +3620,7 @@
         <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>76</v>
@@ -3828,13 +3629,13 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3861,11 +3662,13 @@
         <v>76</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>202</v>
+        <v>76</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>76</v>
@@ -3883,34 +3686,32 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>203</v>
+        <v>153</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>76</v>
       </c>
@@ -3922,7 +3723,7 @@
         <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>76</v>
@@ -3931,13 +3732,13 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3988,30 +3789,30 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4022,7 +3823,7 @@
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>76</v>
@@ -4034,13 +3835,13 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4079,42 +3880,42 @@
         <v>76</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>206</v>
+        <v>155</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4122,10 +3923,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>76</v>
@@ -4137,22 +3938,24 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>76</v>
@@ -4182,42 +3985,42 @@
         <v>76</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>207</v>
+        <v>156</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4225,7 +4028,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>82</v>
@@ -4240,24 +4043,22 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>204</v>
+        <v>76</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>76</v>
@@ -4287,31 +4088,29 @@
         <v>76</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>99</v>
@@ -4319,12 +4118,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>208</v>
+        <v>157</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="C31" s="2"/>
+      <c r="C31" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>76</v>
       </c>
@@ -4348,7 +4149,7 @@
         <v>83</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>209</v>
+        <v>159</v>
       </c>
       <c r="M31" t="s" s="2">
         <v>119</v>
@@ -4422,13 +4223,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>76</v>
@@ -4527,7 +4328,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>212</v>
+        <v>162</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>106</v>
@@ -4630,7 +4431,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>213</v>
+        <v>163</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>108</v>
@@ -4733,7 +4534,7 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>110</v>
@@ -4776,7 +4577,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>76</v>
@@ -4838,7 +4639,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>117</v>
@@ -4867,7 +4668,7 @@
         <v>83</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>216</v>
+        <v>118</v>
       </c>
       <c r="M36" t="s" s="2">
         <v>119</v>
@@ -4909,16 +4710,14 @@
         <v>76</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="AC36" s="2"/>
       <c r="AD36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>120</v>
@@ -4941,13 +4740,13 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>218</v>
+        <v>158</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>76</v>
@@ -4960,7 +4759,7 @@
         <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>76</v>
@@ -4969,13 +4768,13 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>28</v>
+        <v>167</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5026,32 +4825,34 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>219</v>
+        <v>168</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>76</v>
       </c>
@@ -5063,7 +4864,7 @@
         <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>76</v>
@@ -5072,13 +4873,13 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5129,30 +4930,30 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5163,7 +4964,7 @@
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>76</v>
@@ -5175,13 +4976,13 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5220,42 +5021,42 @@
         <v>76</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5263,10 +5064,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>76</v>
@@ -5278,24 +5079,22 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>218</v>
+        <v>76</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>76</v>
@@ -5325,42 +5124,42 @@
         <v>76</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>222</v>
+        <v>172</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5368,7 +5167,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>82</v>
@@ -5383,22 +5182,24 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>223</v>
+        <v>112</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>76</v>
@@ -5440,19 +5241,19 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>99</v>
@@ -5460,14 +5261,12 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>76</v>
       </c>
@@ -5479,7 +5278,7 @@
         <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>76</v>
@@ -5488,13 +5287,13 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>90</v>
+        <v>174</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5533,44 +5332,44 @@
         <v>76</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>76</v>
       </c>
@@ -5591,15 +5390,17 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>119</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -5648,7 +5449,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -5657,23 +5458,25 @@
         <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>227</v>
+        <v>179</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>76</v>
       </c>
@@ -5682,10 +5485,10 @@
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>76</v>
@@ -5739,16 +5542,16 @@
         <v>76</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>97</v>
@@ -5771,10 +5574,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5782,7 +5585,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>82</v>
@@ -5797,24 +5600,22 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>225</v>
+        <v>76</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>76</v>
@@ -5856,10 +5657,10 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>82</v>
@@ -5871,15 +5672,15 @@
         <v>76</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5890,7 +5691,7 @@
         <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>76</v>
@@ -5902,13 +5703,13 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>230</v>
+        <v>28</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5947,58 +5748,56 @@
         <v>76</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>231</v>
+        <v>183</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>76</v>
@@ -6007,22 +5806,24 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>76</v>
@@ -6064,30 +5865,30 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6110,13 +5911,13 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6155,19 +5956,17 @@
         <v>76</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6176,23 +5975,25 @@
         <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>76</v>
       </c>
@@ -6201,7 +6002,7 @@
         <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>76</v>
@@ -6213,15 +6014,17 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>90</v>
+        <v>174</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>119</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>76</v>
@@ -6258,53 +6061,55 @@
         <v>76</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>235</v>
+        <v>188</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>76</v>
@@ -6316,24 +6121,22 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>232</v>
+        <v>76</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>76</v>
@@ -6375,30 +6178,30 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>236</v>
+        <v>190</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6421,17 +6224,15 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>184</v>
+        <v>83</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>237</v>
+        <v>84</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>76</v>
@@ -6480,7 +6281,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -6489,25 +6290,23 @@
         <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>239</v>
+        <v>191</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>76</v>
       </c>
@@ -6516,10 +6315,10 @@
         <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>76</v>
@@ -6573,16 +6372,16 @@
         <v>76</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>97</v>
@@ -6605,10 +6404,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>241</v>
+        <v>192</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6616,7 +6415,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>82</v>
@@ -6631,22 +6430,24 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>76</v>
+        <v>189</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>76</v>
@@ -6688,10 +6489,10 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>82</v>
@@ -6703,15 +6504,15 @@
         <v>76</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>242</v>
+        <v>193</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6722,7 +6523,7 @@
         <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>76</v>
@@ -6734,13 +6535,13 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>90</v>
+        <v>194</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6779,42 +6580,42 @@
         <v>76</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>243</v>
+        <v>115</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6854,7 +6655,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>240</v>
+        <v>3</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>76</v>
@@ -6916,10 +6717,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>244</v>
+        <v>120</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6930,7 +6731,7 @@
         <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>76</v>
@@ -6942,17 +6743,15 @@
         <v>76</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>245</v>
+        <v>118</v>
       </c>
       <c r="M56" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="N56" t="s" s="2">
-        <v>246</v>
-      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -7019,735 +6818,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="D57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AK63">
+  <autoFilter ref="A1:AK56">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7757,7 +6829,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI62">
+  <conditionalFormatting sqref="A2:AI55">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:33:21+00:00</t>
+    <t>2023-04-13T08:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:34:34+00:00</t>
+    <t>2023-04-13T08:54:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:54:00+00:00</t>
+    <t>2023-04-13T09:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T09:51:53+00:00</t>
+    <t>2023-04-13T10:21:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T10:21:56+00:00</t>
+    <t>2023-04-13T12:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T12:58:26+00:00</t>
+    <t>2023-04-13T15:00:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:00:08+00:00</t>
+    <t>2023-04-13T15:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:16:05+00:00</t>
+    <t>2023-04-14T12:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:31:23+00:00</t>
+    <t>2023-04-14T12:45:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:45:28+00:00</t>
+    <t>2023-04-14T13:02:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:02:26+00:00</t>
+    <t>2023-04-14T13:12:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:12:31+00:00</t>
+    <t>2023-04-17T08:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:15:24+00:00</t>
+    <t>2023-04-17T08:17:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:17:23+00:00</t>
+    <t>2023-04-17T08:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:37:32+00:00</t>
+    <t>2023-04-17T09:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T09:07:20+00:00</t>
+    <t>2023-04-17T10:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:39:40+00:00</t>
+    <t>2023-04-17T10:56:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:56:20+00:00</t>
+    <t>2023-04-17T11:14:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:14:19+00:00</t>
+    <t>2023-04-17T11:17:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:17:21+00:00</t>
+    <t>2023-04-17T11:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:39:02+00:00</t>
+    <t>2023-04-17T11:54:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:54:58+00:00</t>
+    <t>2023-04-17T12:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:02:32+00:00</t>
+    <t>2023-04-17T13:37:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T13:37:35+00:00</t>
+    <t>2023-04-17T14:05:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T14:05:09+00:00</t>
+    <t>2023-04-20T17:39:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:39:34+00:00</t>
+    <t>2023-04-20T17:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:42:03+00:00</t>
+    <t>2023-04-20T17:43:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:10+00:00</t>
+    <t>2023-04-20T17:43:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:52+00:00</t>
+    <t>2023-04-28T11:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:09:12+00:00</t>
+    <t>2023-04-28T15:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T15:03:41+00:00</t>
+    <t>2023-04-28T18:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:35:22+00:00</t>
+    <t>2023-04-28T18:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:37:07+00:00</t>
+    <t>2023-04-28T18:58:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:58:16+00:00</t>
+    <t>2023-05-02T06:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:31:09+00:00</t>
+    <t>2023-05-02T06:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:34:44+00:00</t>
+    <t>2023-05-02T07:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T07:22:02+00:00</t>
+    <t>2023-05-02T14:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:04:27+00:00</t>
+    <t>2023-05-02T14:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:10:11+00:00</t>
+    <t>2023-05-02T14:20:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:20:51+00:00</t>
+    <t>2023-05-02T14:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:32:14+00:00</t>
+    <t>2023-05-02T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T15:50:41+00:00</t>
+    <t>2023-05-02T16:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T16:15:55+00:00</t>
+    <t>2023-05-02T17:25:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$56</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="195">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:25:18+00:00</t>
+    <t>2023-05-02T17:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -329,9 +326,6 @@
   </si>
   <si>
     <t>value</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t>BAL MSS</t>
@@ -751,21 +745,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1109,7 +1088,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>28</v>
       </c>
@@ -1212,7 +1191,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>81</v>
       </c>
@@ -1315,7 +1294,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>88</v>
       </c>
@@ -1420,7 +1399,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>100</v>
       </c>
@@ -1441,7 +1420,7 @@
         <v>82</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>76</v>
@@ -1453,10 +1432,10 @@
         <v>90</v>
       </c>
       <c r="L5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1525,12 +1504,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1628,12 +1607,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1662,7 +1641,7 @@
         <v>28</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1731,12 +1710,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1759,16 +1738,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1818,7 +1797,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>82</v>
@@ -1836,12 +1815,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1867,10 +1846,10 @@
         <v>83</v>
       </c>
       <c r="L9" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1921,7 +1900,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -1933,21 +1912,21 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>76</v>
@@ -1960,7 +1939,7 @@
         <v>82</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>76</v>
@@ -1975,7 +1954,7 @@
         <v>28</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2044,12 +2023,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2147,12 +2126,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2181,7 +2160,7 @@
         <v>28</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2250,12 +2229,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2278,16 +2257,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2295,7 +2274,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>76</v>
@@ -2337,7 +2316,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>82</v>
@@ -2355,12 +2334,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2383,13 +2362,13 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2428,17 +2407,17 @@
         <v>76</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2450,21 +2429,21 @@
         <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>76</v>
@@ -2486,13 +2465,13 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2519,14 +2498,14 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="Z15" t="s" s="2">
-        <v>136</v>
-      </c>
       <c r="AA15" t="s" s="2">
         <v>76</v>
       </c>
@@ -2543,7 +2522,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2555,21 +2534,21 @@
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>76</v>
@@ -2582,7 +2561,7 @@
         <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>76</v>
@@ -2597,7 +2576,7 @@
         <v>28</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2666,12 +2645,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2769,12 +2748,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2803,7 +2782,7 @@
         <v>28</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2872,12 +2851,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2900,16 +2879,16 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -2917,7 +2896,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>76</v>
@@ -2959,7 +2938,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -2977,12 +2956,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3008,10 +2987,10 @@
         <v>83</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3062,7 +3041,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3074,21 +3053,21 @@
         <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>76</v>
@@ -3101,7 +3080,7 @@
         <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>76</v>
@@ -3116,7 +3095,7 @@
         <v>28</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3185,12 +3164,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3288,12 +3267,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3322,7 +3301,7 @@
         <v>28</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3391,12 +3370,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3419,16 +3398,16 @@
         <v>76</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3436,7 +3415,7 @@
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>76</v>
@@ -3478,7 +3457,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -3496,12 +3475,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3527,10 +3506,10 @@
         <v>83</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3581,7 +3560,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3593,21 +3572,21 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>76</v>
@@ -3620,7 +3599,7 @@
         <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>76</v>
@@ -3635,7 +3614,7 @@
         <v>28</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3704,12 +3683,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3807,12 +3786,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3841,7 +3820,7 @@
         <v>28</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3910,12 +3889,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3938,16 +3917,16 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -3955,7 +3934,7 @@
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>76</v>
@@ -3997,7 +3976,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -4015,12 +3994,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4046,10 +4025,10 @@
         <v>83</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4088,17 +4067,17 @@
         <v>76</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4110,21 +4089,21 @@
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="C31" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>76</v>
@@ -4149,10 +4128,10 @@
         <v>83</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4203,7 +4182,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4215,21 +4194,21 @@
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>76</v>
@@ -4242,7 +4221,7 @@
         <v>82</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>76</v>
@@ -4257,7 +4236,7 @@
         <v>28</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4326,12 +4305,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4429,12 +4408,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4463,7 +4442,7 @@
         <v>28</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4532,12 +4511,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4560,16 +4539,16 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -4577,7 +4556,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>76</v>
@@ -4619,7 +4598,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -4637,12 +4616,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4668,10 +4647,10 @@
         <v>83</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4710,17 +4689,17 @@
         <v>76</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AC36" s="2"/>
       <c r="AD36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -4732,21 +4711,21 @@
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>76</v>
@@ -4771,10 +4750,10 @@
         <v>83</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4825,7 +4804,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -4837,21 +4816,21 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>76</v>
@@ -4864,7 +4843,7 @@
         <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>76</v>
@@ -4879,7 +4858,7 @@
         <v>28</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4948,12 +4927,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5051,12 +5030,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5085,7 +5064,7 @@
         <v>28</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5154,12 +5133,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5182,16 +5161,16 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5199,7 +5178,7 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>76</v>
@@ -5241,7 +5220,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -5259,12 +5238,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5287,13 +5266,13 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5332,17 +5311,17 @@
         <v>76</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -5354,21 +5333,21 @@
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="C43" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>76</v>
@@ -5390,16 +5369,16 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5449,7 +5428,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -5461,21 +5440,21 @@
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>76</v>
@@ -5488,7 +5467,7 @@
         <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>76</v>
@@ -5503,7 +5482,7 @@
         <v>28</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5572,12 +5551,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5675,12 +5654,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5709,7 +5688,7 @@
         <v>28</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5778,12 +5757,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5806,16 +5785,16 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -5823,7 +5802,7 @@
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>76</v>
@@ -5865,7 +5844,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -5883,12 +5862,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5911,13 +5890,13 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -5956,17 +5935,17 @@
         <v>76</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -5978,21 +5957,21 @@
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>76</v>
@@ -6014,16 +5993,16 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6073,7 +6052,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -6085,21 +6064,21 @@
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>76</v>
@@ -6127,7 +6106,7 @@
         <v>28</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6196,12 +6175,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6299,12 +6278,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6333,7 +6312,7 @@
         <v>28</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6402,12 +6381,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6430,16 +6409,16 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6447,7 +6426,7 @@
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>76</v>
@@ -6489,7 +6468,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -6507,12 +6486,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6535,13 +6514,13 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6592,7 +6571,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -6604,18 +6583,18 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6638,16 +6617,16 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -6697,7 +6676,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -6715,12 +6694,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6743,13 +6722,13 @@
         <v>76</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -6800,7 +6779,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -6812,31 +6791,13 @@
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>99</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK56">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI55">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-mailbox-mss.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:45:11+00:00</t>
+    <t>2023-05-02T17:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
